--- a/model_data.xlsx
+++ b/model_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
           <t>Logo_URL</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Params_Verified</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -468,11 +473,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -488,6 +493,9 @@
         <is>
           <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/OpenAI_Logo.svg</t>
         </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -519,6 +527,9 @@
           <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/stepfun-color.png</t>
         </is>
       </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,20 +560,23 @@
           <t>https://avatars.githubusercontent.com/u/89920319?s=400&amp;v=4</t>
         </is>
       </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Qwen2.5-VL</t>
+          <t>DeepSeek-VL2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -571,28 +585,31 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/qwen-color.png</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/deepseek-color.png</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DeepSeek-VL2</t>
+          <t>DeepSeek-V3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -608,36 +625,42 @@
         <is>
           <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/deepseek-color.png</t>
         </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude 4 Opus</t>
+          <t>Qwen2.5-VL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1000</v>
+        <v>72</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Domestic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://dl.svgcdn.com/svg/logos/anthropic-icon.svg</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/qwen-color.png</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -648,7 +671,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -669,6 +692,9 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/Meta_Platforms_Inc._logo.svg</t>
         </is>
       </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -678,7 +704,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -699,20 +725,23 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/Meta_Platforms_Inc._logo.svg</t>
         </is>
       </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>Claude 4 Opus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -721,13 +750,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/OpenAI_Logo.svg</t>
-        </is>
+          <t>https://dl.svgcdn.com/svg/logos/anthropic-icon.svg</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -759,50 +791,56 @@
           <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/internlm-color.png</t>
         </is>
       </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>InternVL 3.5</t>
+          <t>GPT-5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>241</v>
+        <v>1500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Domestic</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>InternVL</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/internlm-color.png</t>
-        </is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/OpenAI_Logo.svg</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kimi K2.5</t>
+          <t>InternVL 3.5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1000</v>
+        <v>241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -811,13 +849,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kimi</t>
+          <t>InternVL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/kimi-color.png</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/internlm-color.png</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -828,7 +869,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -849,16 +890,19 @@
           <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/qwen-color.png</t>
         </is>
       </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro</t>
+          <t>Kimi K2.5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -866,18 +910,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Domestic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Kimi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c1/Google_%22G%22_logo.svg</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/kimi-color.png</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -888,7 +935,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -909,20 +956,23 @@
           <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/zhipu-color.png</t>
         </is>
       </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Qwen3.5</t>
+          <t>Doubao 2.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>397</v>
+        <v>500</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -931,28 +981,31 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/qwen-color.png</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/doubao-color.png</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Doubao 2.0</t>
+          <t>Qwen3.5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>500</v>
+        <v>397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -961,28 +1014,31 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/doubao-color.png</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/qwen-color.png</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claude 5</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -991,73 +1047,181 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://dl.svgcdn.com/svg/logos/anthropic-icon.svg</t>
-        </is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c1/Google_%22G%22_logo.svg</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GPT-5.3</t>
+          <t>MiniMax M2.7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1500</v>
+        <v>230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Domestic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/OpenAI_Logo.svg</t>
-        </is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/minimax-color.png</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GLM-6 Pro</t>
+          <t>GPT-5.5 Pro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Domestic</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GLM</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/zhipu-color.png</t>
-        </is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/OpenAI_Logo.svg</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Domestic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/deepseek-color.png</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Qwen 3.7 Max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>500</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Domestic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://unpkg.com/@lobehub/icons-static-png@latest/light/qwen-color.png</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://dl.svgcdn.com/svg/logos/anthropic-icon.svg</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
